--- a/output/graficos_nacionales/plot_nacional_e_supneta_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_supneta_a_2022.xlsx
@@ -462,7 +462,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3820,7 +3820,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -6580,7 +6580,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -7270,7 +7270,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -7684,7 +7684,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -7960,7 +7960,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -8144,7 +8144,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -8696,7 +8696,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -9156,7 +9156,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -9616,7 +9616,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -10076,7 +10076,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -10214,7 +10214,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -10352,7 +10352,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -10398,7 +10398,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -10490,7 +10490,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -10582,7 +10582,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -10812,7 +10812,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -10996,7 +10996,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -11180,7 +11180,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -11318,7 +11318,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -11456,7 +11456,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -11502,7 +11502,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -11640,7 +11640,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -11732,7 +11732,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -11916,7 +11916,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -12008,7 +12008,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -12100,7 +12100,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -12192,7 +12192,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -12238,7 +12238,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -12284,7 +12284,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -12468,7 +12468,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -12514,7 +12514,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -12606,7 +12606,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -12652,7 +12652,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -12790,7 +12790,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -12836,7 +12836,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -12882,7 +12882,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -12928,7 +12928,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -13020,7 +13020,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -13066,7 +13066,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -13204,7 +13204,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -13250,7 +13250,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -13342,7 +13342,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -13388,7 +13388,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -13434,7 +13434,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -13480,7 +13480,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -13526,7 +13526,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -13756,7 +13756,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -13986,7 +13986,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -14032,7 +14032,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -14124,7 +14124,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -14170,7 +14170,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -14354,7 +14354,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -14400,7 +14400,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -14446,7 +14446,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -14722,7 +14722,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -14814,7 +14814,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -15182,7 +15182,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -15228,7 +15228,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">

--- a/output/graficos_nacionales/plot_nacional_e_supneta_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_supneta_a_2022.xlsx
@@ -2065,7 +2065,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 15:48</t>
+    <t xml:space="preserve">2026-09-07 12:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_e_supneta_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_supneta_a_2022.xlsx
@@ -2065,7 +2065,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 12:53</t>
+    <t xml:space="preserve">2026-09-08 10:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
